--- a/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="8475" windowHeight="11175" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="禅意" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
   <si>
     <t>名称</t>
   </si>
@@ -48,63 +48,54 @@
     <t>雪庐草人2</t>
   </si>
   <si>
-    <t>雪庐草人3</t>
-  </si>
-  <si>
     <t>长耳庄巧姑</t>
   </si>
   <si>
     <t>连击</t>
   </si>
   <si>
+    <t>符文·雄鹿之道</t>
+  </si>
+  <si>
     <t>小计：</t>
   </si>
   <si>
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>蟠桃隐士</t>
-  </si>
-  <si>
-    <t>传记·月落</t>
+    <t>植甲师</t>
   </si>
   <si>
     <t>宫廷乐师</t>
   </si>
   <si>
-    <t>雪山飞狐</t>
-  </si>
-  <si>
     <t>百刺浪客</t>
   </si>
   <si>
-    <t>黑竹林地</t>
+    <t>白鹿贤士</t>
+  </si>
+  <si>
+    <t>萌化术</t>
   </si>
   <si>
     <t>渡船隐士</t>
   </si>
   <si>
-    <t>万物之灵1</t>
-  </si>
-  <si>
-    <t>万物之灵2</t>
-  </si>
-  <si>
     <t>紫色卡等：</t>
   </si>
   <si>
     <t>流岚刃·琳</t>
   </si>
   <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
     <t>悟能禅杖</t>
   </si>
   <si>
     <t>雪域春光·凛</t>
   </si>
   <si>
+    <t>三熊阵</t>
+  </si>
+  <si>
     <t>逍遥居士·铭</t>
   </si>
   <si>
@@ -120,6 +111,15 @@
     <t>禅意卡等：</t>
   </si>
   <si>
+    <t>圣殿斥候</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>天使琼浆</t>
+  </si>
+  <si>
     <t>炫目神光</t>
   </si>
   <si>
@@ -138,24 +138,15 @@
     <t>光明惩戒2</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
     <t>圣殿御卫</t>
   </si>
   <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
     <t>召集护卫</t>
   </si>
   <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
@@ -165,9 +156,6 @@
     <t>明日之音·露娜</t>
   </si>
   <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
@@ -183,10 +171,10 @@
     <t>寒风草人</t>
   </si>
   <si>
-    <t>阴冷墓穴</t>
-  </si>
-  <si>
-    <t>寒冬将至</t>
+    <t>寒冬将至1</t>
+  </si>
+  <si>
+    <t>寒冬将至2</t>
   </si>
   <si>
     <t>神庙魔像</t>
@@ -198,10 +186,16 @@
     <t>灵魂抽取</t>
   </si>
   <si>
+    <t>符文·天寒地冻</t>
+  </si>
+  <si>
+    <t>寒冰骨墙</t>
+  </si>
+  <si>
     <t>冰峰甲虫</t>
   </si>
   <si>
-    <t>咒杀酷吏</t>
+    <t>冬幕骑士</t>
   </si>
   <si>
     <t>寒风血刃</t>
@@ -219,22 +213,16 @@
     <t>洞悉之眼2</t>
   </si>
   <si>
-    <t>洞悉之眼3</t>
-  </si>
-  <si>
-    <t>电流激活</t>
-  </si>
-  <si>
     <t>学仆-观测型</t>
   </si>
   <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
-  </si>
-  <si>
-    <t>沉重否定3</t>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
   </si>
   <si>
     <t>破魔系教授</t>
@@ -246,13 +234,13 @@
     <t>克隆术2</t>
   </si>
   <si>
-    <t>学仆-脉冲型</t>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
   </si>
   <si>
     <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>心灵操控</t>
   </si>
   <si>
     <t>No.2时光·米拉</t>
@@ -1222,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1230,7 +1218,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1252,7 +1240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1263,45 +1251,45 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1315,11 +1303,11 @@
       </c>
       <c r="C9" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1327,10 +1315,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1338,32 +1326,32 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1371,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1379,65 +1367,65 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>18</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>16</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C12:C17)</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C12:C20)</f>
-        <v>17.8888888888889</v>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1445,10 +1433,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1456,10 +1444,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1467,77 +1455,44 @@
         <v>22</v>
       </c>
       <c r="B28" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C28" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="3">
-        <v>4</v>
-      </c>
-      <c r="C29" s="3">
-        <v>18</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="3">
-        <v>5</v>
-      </c>
-      <c r="C30" s="3">
-        <v>19</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C23:C28)</f>
+        <v>19.1666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="3">
-        <v>6</v>
-      </c>
-      <c r="C31" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="3">
-        <f>AVERAGE(C26:C31)</f>
-        <v>19.1666666666667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4">
-        <f>AVERAGE(C2:C6,C12:C20,C26:C31)</f>
-        <v>19.05</v>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C6,C12:C17,C23:C28)</f>
+        <v>18.9411764705882</v>
       </c>
     </row>
   </sheetData>
@@ -1549,7 +1504,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1557,7 +1512,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1568,159 +1523,159 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>20.1666666666667</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>20.4444444444444</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="B16" s="2">
         <v>2</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1738,27 +1693,27 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2">
-        <f>AVERAGE(C13:C18)</f>
-        <v>19.6666666666667</v>
+        <f>AVERAGE(C16:C18)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -1769,7 +1724,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1780,36 +1735,30 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B28" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="3">
-        <v>8</v>
-      </c>
-      <c r="C29" s="3">
-        <v>17</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3"/>
@@ -1817,32 +1766,27 @@
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
+      <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="3">
-        <f>AVERAGE(C24:C29)</f>
-        <v>17.3333333333333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="4">
-        <f>AVERAGE(C2:C7,C13:C18,C24:C29)</f>
-        <v>19.0555555555556</v>
+      <c r="B31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C24:C28)</f>
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C10,C16:C18,C24:C28)</f>
+        <v>19.5294117647059</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1798,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1862,7 +1806,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1873,53 +1817,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1928,20 +1872,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1950,12 +1894,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1969,108 +1913,130 @@
       </c>
       <c r="C11" s="1">
         <f>AVERAGE(C2:C8)</f>
-        <v>18.4285714285714</v>
+        <v>18.5714285714286</v>
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C14:C17)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="2">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="2">
-        <f>AVERAGE(C14:C15)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3">
+        <f>AVERAGE(C23:C24)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="3">
-        <v>3</v>
-      </c>
-      <c r="C21" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="3">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="3">
-        <f>AVERAGE(C21:C22)</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="4">
-        <f>AVERAGE(C2:C8,C14:C15,C21:C22)</f>
-        <v>18.5454545454545</v>
+      <c r="C30" s="4">
+        <f>AVERAGE(C2:C8,C14:C17,C23:C24)</f>
+        <v>17.6923076923077</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2056,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2101,20 +2067,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -2123,109 +2089,109 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>18.1666666666667</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>13.375</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2236,46 +2202,46 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
       </c>
       <c r="C20" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2293,22 +2259,22 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C15:C20)</f>
-        <v>14.5</v>
+        <f>AVERAGE(C13:C20)</f>
+        <v>16.375</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2326,23 +2292,23 @@
         <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C20,C26:C26)</f>
-        <v>13.7333333333333</v>
+        <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8475" windowHeight="11175" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="11190" windowHeight="9990" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="禅意" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
   <si>
     <t>名称</t>
   </si>
@@ -42,19 +42,25 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
     <t>雪庐草人1</t>
   </si>
   <si>
     <t>雪庐草人2</t>
   </si>
   <si>
+    <t>飓风术</t>
+  </si>
+  <si>
     <t>长耳庄巧姑</t>
   </si>
   <si>
     <t>连击</t>
   </si>
   <si>
-    <t>符文·雄鹿之道</t>
+    <t>符文·疾风图腾</t>
   </si>
   <si>
     <t>小计：</t>
@@ -63,10 +69,7 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>植甲师</t>
-  </si>
-  <si>
-    <t>宫廷乐师</t>
+    <t>蟠桃隐士</t>
   </si>
   <si>
     <t>百刺浪客</t>
@@ -75,7 +78,7 @@
     <t>白鹿贤士</t>
   </si>
   <si>
-    <t>萌化术</t>
+    <t>墨轩隐士</t>
   </si>
   <si>
     <t>渡船隐士</t>
@@ -87,18 +90,18 @@
     <t>流岚刃·琳</t>
   </si>
   <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>雪域春光·凛</t>
+  </si>
+  <si>
+    <t>三熊阵</t>
+  </si>
+  <si>
     <t>悟能禅杖</t>
   </si>
   <si>
-    <t>雪域春光·凛</t>
-  </si>
-  <si>
-    <t>三熊阵</t>
-  </si>
-  <si>
-    <t>逍遥居士·铭</t>
-  </si>
-  <si>
     <t>豪情禅师·悟能</t>
   </si>
   <si>
@@ -120,22 +123,22 @@
     <t>天使琼浆</t>
   </si>
   <si>
-    <t>炫目神光</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
+    <t>炫目神光1</t>
+  </si>
+  <si>
+    <t>炫目神光2</t>
   </si>
   <si>
     <t>增援战线</t>
   </si>
   <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>光明惩戒1</t>
-  </si>
-  <si>
-    <t>光明惩戒2</t>
+    <t>田园守望者1</t>
+  </si>
+  <si>
+    <t>田园守望者2</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
   </si>
   <si>
     <t>圣殿御卫</t>
@@ -150,18 +153,12 @@
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
     <t>帝国卡等：</t>
   </si>
   <si>
@@ -180,16 +177,22 @@
     <t>神庙魔像</t>
   </si>
   <si>
-    <t>极地狂信者</t>
-  </si>
-  <si>
-    <t>灵魂抽取</t>
+    <t>极地狂信者1</t>
+  </si>
+  <si>
+    <t>极地狂信者2</t>
+  </si>
+  <si>
+    <t>灵魂抽取1</t>
+  </si>
+  <si>
+    <t>灵魂抽取2</t>
   </si>
   <si>
     <t>符文·天寒地冻</t>
   </si>
   <si>
-    <t>寒冰骨墙</t>
+    <t>寒彻骨</t>
   </si>
   <si>
     <t>冰峰甲虫</t>
@@ -207,13 +210,13 @@
     <t>冬神卡等：</t>
   </si>
   <si>
-    <t>洞悉之眼1</t>
-  </si>
-  <si>
-    <t>洞悉之眼2</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
+    <t>学仆-观测型1</t>
+  </si>
+  <si>
+    <t>学仆-观测型2</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
   </si>
   <si>
     <t>沉重否定</t>
@@ -238,6 +241,9 @@
   </si>
   <si>
     <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
   </si>
   <si>
     <t>米拉方舟</t>
@@ -1210,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1256,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>22</v>
@@ -1267,10 +1273,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1278,66 +1284,66 @@
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>20.4</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>14</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>20.1428571428571</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1348,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1359,7 +1365,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1367,16 +1373,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1384,26 +1396,20 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C12:C17)</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>20</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>19.8</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1411,7 +1417,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
         <v>20</v>
@@ -1436,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1444,10 +1450,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1455,16 +1461,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="3">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3">
         <v>6</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3"/>
@@ -1472,27 +1484,32 @@
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C23:C28)</f>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="3">
+        <f>AVERAGE(C24:C29)</f>
         <v>19.1666666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="4" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C6,C12:C17,C23:C28)</f>
-        <v>18.9411764705882</v>
+      <c r="B35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="4">
+        <f>AVERAGE(C2:C8,C14:C18,C24:C29)</f>
+        <v>19.7222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1521,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1525,29 +1542,29 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1558,29 +1575,29 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1591,7 +1608,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1602,10 +1619,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -1613,13 +1630,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1634,42 +1651,42 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
-        <v>20.4444444444444</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
         <v>6</v>
@@ -1690,10 +1707,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C16:C18)</f>
@@ -1702,7 +1719,7 @@
     </row>
     <row r="24" ht="14" customHeight="1" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -1713,80 +1730,58 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3">
-        <v>6</v>
-      </c>
-      <c r="C27" s="3">
-        <v>20</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C24:C26)</f>
+        <v>17.3333333333333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3">
-        <v>8</v>
-      </c>
-      <c r="C28" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C24:C28)</f>
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C10,C16:C18,C24:C28)</f>
-        <v>19.5294117647059</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>
+        <v>19.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1793,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1819,7 +1814,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1830,7 +1825,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1841,18 +1836,18 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1863,7 +1858,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1874,169 +1869,191 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>18.5714285714286</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>14</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>18.5555555555556</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B18" s="2">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>16</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C14:C17)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2">
+        <f>AVERAGE(C16:C19)</f>
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="3">
         <v>3</v>
       </c>
-      <c r="C23" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="C25" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="3">
         <v>5</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C26" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-    </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3">
-        <f>AVERAGE(C23:C24)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="4">
-        <f>AVERAGE(C2:C8,C14:C17,C23:C24)</f>
-        <v>17.6923076923077</v>
+      <c r="C29" s="3">
+        <f>AVERAGE(C25:C26)</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
+        <v>18.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2069,69 +2086,63 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
@@ -2139,48 +2150,54 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>18.1666666666667</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -2191,18 +2208,18 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -2213,35 +2230,35 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2">
         <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
       </c>
       <c r="C20" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2256,25 +2273,25 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C13:C20)</f>
-        <v>16.375</v>
+        <f>AVERAGE(C12:C20)</f>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2289,26 +2306,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>17</v>
+        <f>AVERAGE(C2:C6,C12:C20,C26:C26)</f>
+        <v>18.0666666666667</v>
       </c>
     </row>
   </sheetData>
